--- a/artfynd/A 6809-2026 artfynd.xlsx
+++ b/artfynd/A 6809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3242,6 +3242,1961 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131931053</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78933</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>353</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>473669</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6874215</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131930258</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>473992</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6874187</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131931458</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>473600</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6874121</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131931837</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78933</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>353</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>473660</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6874061</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131931861</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>473689</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6874040</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131932091</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58064</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>473755</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6874002</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131931505</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79857</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>473596</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6874121</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131931404</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78274</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>473585</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6874134</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131932307</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79299</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>185</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>473802</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6874032</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131931410</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79857</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>473585</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6874134</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131930967</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>473719</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6874196</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131931334</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78933</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>353</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>473561</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6874174</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131931945</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79886</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>473714</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6874034</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131931681</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80372</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>473660</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6874125</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131929938</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80372</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>474075</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6874149</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Mycket gammal sälgklon.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131932057</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79346</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>864</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>473764</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6874014</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131930107</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>474008</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6874146</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131931528</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78933</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>353</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>473602</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6874119</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131930506</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>473888</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6874110</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131931872</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>473711</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6874032</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6809-2026 artfynd.xlsx
+++ b/artfynd/A 6809-2026 artfynd.xlsx
@@ -3831,10 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131931505</v>
+        <v>131932307</v>
       </c>
       <c r="B33" t="n">
-        <v>79857</v>
+        <v>79299</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,21 +3842,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473596</v>
+        <v>473802</v>
       </c>
       <c r="R33" t="n">
-        <v>6874121</v>
+        <v>6874032</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131931404</v>
+        <v>131931505</v>
       </c>
       <c r="B34" t="n">
-        <v>78274</v>
+        <v>79857</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,21 +3939,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473585</v>
+        <v>473596</v>
       </c>
       <c r="R34" t="n">
-        <v>6874134</v>
+        <v>6874121</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4025,10 +4025,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131932307</v>
+        <v>131931404</v>
       </c>
       <c r="B35" t="n">
-        <v>79299</v>
+        <v>78274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,21 +4036,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473802</v>
+        <v>473585</v>
       </c>
       <c r="R35" t="n">
-        <v>6874032</v>
+        <v>6874134</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>

--- a/artfynd/A 6809-2026 artfynd.xlsx
+++ b/artfynd/A 6809-2026 artfynd.xlsx
@@ -3341,7 +3341,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131930258</v>
+        <v>131931458</v>
       </c>
       <c r="B28" t="n">
         <v>79267</v>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473992</v>
+        <v>473600</v>
       </c>
       <c r="R28" t="n">
-        <v>6874187</v>
+        <v>6874121</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131931458</v>
+        <v>131930258</v>
       </c>
       <c r="B29" t="n">
         <v>79267</v>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473600</v>
+        <v>473992</v>
       </c>
       <c r="R29" t="n">
-        <v>6874121</v>
+        <v>6874187</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 6809-2026 artfynd.xlsx
+++ b/artfynd/A 6809-2026 artfynd.xlsx
@@ -3341,7 +3341,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131931458</v>
+        <v>131930258</v>
       </c>
       <c r="B28" t="n">
         <v>79267</v>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473600</v>
+        <v>473992</v>
       </c>
       <c r="R28" t="n">
-        <v>6874121</v>
+        <v>6874187</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131930258</v>
+        <v>131931458</v>
       </c>
       <c r="B29" t="n">
         <v>79267</v>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473992</v>
+        <v>473600</v>
       </c>
       <c r="R29" t="n">
-        <v>6874187</v>
+        <v>6874121</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3831,10 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131932307</v>
+        <v>131931505</v>
       </c>
       <c r="B33" t="n">
-        <v>79299</v>
+        <v>79857</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,21 +3842,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473802</v>
+        <v>473596</v>
       </c>
       <c r="R33" t="n">
-        <v>6874032</v>
+        <v>6874121</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131931505</v>
+        <v>131931404</v>
       </c>
       <c r="B34" t="n">
-        <v>79857</v>
+        <v>78274</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,21 +3939,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473596</v>
+        <v>473585</v>
       </c>
       <c r="R34" t="n">
-        <v>6874121</v>
+        <v>6874134</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4025,10 +4025,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131931404</v>
+        <v>131932307</v>
       </c>
       <c r="B35" t="n">
-        <v>78274</v>
+        <v>79299</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,21 +4036,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473585</v>
+        <v>473802</v>
       </c>
       <c r="R35" t="n">
-        <v>6874134</v>
+        <v>6874032</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>

--- a/artfynd/A 6809-2026 artfynd.xlsx
+++ b/artfynd/A 6809-2026 artfynd.xlsx
@@ -3247,7 +3247,7 @@
         <v>131931053</v>
       </c>
       <c r="B27" t="n">
-        <v>78933</v>
+        <v>78935</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>131930258</v>
       </c>
       <c r="B28" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>131931458</v>
       </c>
       <c r="B29" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131931837</v>
+        <v>131931861</v>
       </c>
       <c r="B30" t="n">
-        <v>78933</v>
+        <v>79269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,21 +3546,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473660</v>
+        <v>473689</v>
       </c>
       <c r="R30" t="n">
-        <v>6874061</v>
+        <v>6874040</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3632,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131931861</v>
+        <v>131931837</v>
       </c>
       <c r="B31" t="n">
-        <v>79267</v>
+        <v>78935</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,21 +3643,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473689</v>
+        <v>473660</v>
       </c>
       <c r="R31" t="n">
-        <v>6874040</v>
+        <v>6874061</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3732,7 +3732,7 @@
         <v>131932091</v>
       </c>
       <c r="B32" t="n">
-        <v>58064</v>
+        <v>58066</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3831,10 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131932307</v>
+        <v>131931404</v>
       </c>
       <c r="B33" t="n">
-        <v>79299</v>
+        <v>78276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,21 +3842,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473802</v>
+        <v>473585</v>
       </c>
       <c r="R33" t="n">
-        <v>6874032</v>
+        <v>6874134</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131931505</v>
+        <v>131932307</v>
       </c>
       <c r="B34" t="n">
-        <v>79857</v>
+        <v>79301</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,21 +3939,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473596</v>
+        <v>473802</v>
       </c>
       <c r="R34" t="n">
-        <v>6874121</v>
+        <v>6874032</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4025,10 +4025,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131931404</v>
+        <v>131931505</v>
       </c>
       <c r="B35" t="n">
-        <v>78274</v>
+        <v>79859</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,21 +4036,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473585</v>
+        <v>473596</v>
       </c>
       <c r="R35" t="n">
-        <v>6874134</v>
+        <v>6874121</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4125,7 +4125,7 @@
         <v>131931410</v>
       </c>
       <c r="B36" t="n">
-        <v>79857</v>
+        <v>79859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>131930967</v>
       </c>
       <c r="B37" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>131931334</v>
       </c>
       <c r="B38" t="n">
-        <v>78933</v>
+        <v>78935</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>131931945</v>
       </c>
       <c r="B39" t="n">
-        <v>79886</v>
+        <v>79888</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>131931681</v>
       </c>
       <c r="B40" t="n">
-        <v>80372</v>
+        <v>80374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>131929938</v>
       </c>
       <c r="B41" t="n">
-        <v>80372</v>
+        <v>80374</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>131932057</v>
       </c>
       <c r="B42" t="n">
-        <v>79346</v>
+        <v>79348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131930107</v>
       </c>
       <c r="B43" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>131931528</v>
       </c>
       <c r="B44" t="n">
-        <v>78933</v>
+        <v>78935</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>131930506</v>
       </c>
       <c r="B45" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>131931872</v>
       </c>
       <c r="B46" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 6809-2026 artfynd.xlsx
+++ b/artfynd/A 6809-2026 artfynd.xlsx
@@ -3247,7 +3247,7 @@
         <v>131931053</v>
       </c>
       <c r="B27" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131930258</v>
+        <v>131931837</v>
       </c>
       <c r="B28" t="n">
-        <v>79269</v>
+        <v>78940</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473992</v>
+        <v>473660</v>
       </c>
       <c r="R28" t="n">
-        <v>6874187</v>
+        <v>6874061</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131931458</v>
+        <v>131930258</v>
       </c>
       <c r="B29" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473600</v>
+        <v>473992</v>
       </c>
       <c r="R29" t="n">
-        <v>6874121</v>
+        <v>6874187</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131931861</v>
+        <v>131931458</v>
       </c>
       <c r="B30" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473689</v>
+        <v>473600</v>
       </c>
       <c r="R30" t="n">
-        <v>6874040</v>
+        <v>6874121</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3632,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131931837</v>
+        <v>131931861</v>
       </c>
       <c r="B31" t="n">
-        <v>78935</v>
+        <v>79274</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,21 +3643,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473660</v>
+        <v>473689</v>
       </c>
       <c r="R31" t="n">
-        <v>6874061</v>
+        <v>6874040</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3732,7 +3732,7 @@
         <v>131932091</v>
       </c>
       <c r="B32" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3831,10 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131931404</v>
+        <v>131932307</v>
       </c>
       <c r="B33" t="n">
-        <v>78276</v>
+        <v>79306</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,21 +3842,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473585</v>
+        <v>473802</v>
       </c>
       <c r="R33" t="n">
-        <v>6874134</v>
+        <v>6874032</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131932307</v>
+        <v>131931404</v>
       </c>
       <c r="B34" t="n">
-        <v>79301</v>
+        <v>78281</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,21 +3939,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473802</v>
+        <v>473585</v>
       </c>
       <c r="R34" t="n">
-        <v>6874032</v>
+        <v>6874134</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4028,7 +4028,7 @@
         <v>131931505</v>
       </c>
       <c r="B35" t="n">
-        <v>79859</v>
+        <v>79864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>131931410</v>
       </c>
       <c r="B36" t="n">
-        <v>79859</v>
+        <v>79864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>131930967</v>
       </c>
       <c r="B37" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>131931334</v>
       </c>
       <c r="B38" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>131931945</v>
       </c>
       <c r="B39" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>131931681</v>
       </c>
       <c r="B40" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>131929938</v>
       </c>
       <c r="B41" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>131932057</v>
       </c>
       <c r="B42" t="n">
-        <v>79348</v>
+        <v>79353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131930107</v>
       </c>
       <c r="B43" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>131931528</v>
       </c>
       <c r="B44" t="n">
-        <v>78935</v>
+        <v>78940</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>131930506</v>
       </c>
       <c r="B45" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>131931872</v>
       </c>
       <c r="B46" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 6809-2026 artfynd.xlsx
+++ b/artfynd/A 6809-2026 artfynd.xlsx
@@ -3831,10 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131932307</v>
+        <v>131931505</v>
       </c>
       <c r="B33" t="n">
-        <v>79306</v>
+        <v>79864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,21 +3842,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473802</v>
+        <v>473596</v>
       </c>
       <c r="R33" t="n">
-        <v>6874032</v>
+        <v>6874121</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4025,10 +4025,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131931505</v>
+        <v>131932307</v>
       </c>
       <c r="B35" t="n">
-        <v>79864</v>
+        <v>79306</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,21 +4036,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473596</v>
+        <v>473802</v>
       </c>
       <c r="R35" t="n">
-        <v>6874121</v>
+        <v>6874032</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>

--- a/artfynd/A 6809-2026 artfynd.xlsx
+++ b/artfynd/A 6809-2026 artfynd.xlsx
@@ -3247,7 +3247,7 @@
         <v>131931053</v>
       </c>
       <c r="B27" t="n">
-        <v>78940</v>
+        <v>78942</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>131931837</v>
       </c>
       <c r="B28" t="n">
-        <v>78940</v>
+        <v>78942</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>131930258</v>
       </c>
       <c r="B29" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>131931458</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>131931861</v>
       </c>
       <c r="B31" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>131932091</v>
       </c>
       <c r="B32" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3831,10 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131931505</v>
+        <v>131931404</v>
       </c>
       <c r="B33" t="n">
-        <v>79864</v>
+        <v>78283</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,21 +3842,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473596</v>
+        <v>473585</v>
       </c>
       <c r="R33" t="n">
-        <v>6874121</v>
+        <v>6874134</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131931404</v>
+        <v>131932307</v>
       </c>
       <c r="B34" t="n">
-        <v>78281</v>
+        <v>79308</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,21 +3939,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473585</v>
+        <v>473802</v>
       </c>
       <c r="R34" t="n">
-        <v>6874134</v>
+        <v>6874032</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4025,10 +4025,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131932307</v>
+        <v>131931505</v>
       </c>
       <c r="B35" t="n">
-        <v>79306</v>
+        <v>79866</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,21 +4036,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473802</v>
+        <v>473596</v>
       </c>
       <c r="R35" t="n">
-        <v>6874032</v>
+        <v>6874121</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4125,7 +4125,7 @@
         <v>131931410</v>
       </c>
       <c r="B36" t="n">
-        <v>79864</v>
+        <v>79866</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>131930967</v>
       </c>
       <c r="B37" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>131931334</v>
       </c>
       <c r="B38" t="n">
-        <v>78940</v>
+        <v>78942</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>131931945</v>
       </c>
       <c r="B39" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>131931681</v>
       </c>
       <c r="B40" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>131929938</v>
       </c>
       <c r="B41" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>131932057</v>
       </c>
       <c r="B42" t="n">
-        <v>79353</v>
+        <v>79355</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131930107</v>
       </c>
       <c r="B43" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>131931528</v>
       </c>
       <c r="B44" t="n">
-        <v>78940</v>
+        <v>78942</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>131930506</v>
       </c>
       <c r="B45" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>131931872</v>
       </c>
       <c r="B46" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 6809-2026 artfynd.xlsx
+++ b/artfynd/A 6809-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111444632</v>
+        <v>131932307</v>
       </c>
       <c r="B2" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brunnsbäcken, Hjd</t>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473700.3453890086</v>
+        <v>473802</v>
       </c>
       <c r="R2" t="n">
-        <v>6874602.87807036</v>
+        <v>6874032</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111683563</v>
+        <v>119706155</v>
       </c>
       <c r="B3" t="n">
-        <v>90660</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,38 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473804</v>
+        <v>473828</v>
       </c>
       <c r="R3" t="n">
-        <v>6874287</v>
+        <v>6874124</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111683269</v>
+        <v>131931053</v>
       </c>
       <c r="B4" t="n">
-        <v>90660</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,35 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473503</v>
+        <v>473669</v>
       </c>
       <c r="R4" t="n">
-        <v>6874253</v>
+        <v>6874215</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -962,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111682968</v>
+        <v>131931334</v>
       </c>
       <c r="B5" t="n">
-        <v>90660</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,38 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473689</v>
+        <v>473561</v>
       </c>
       <c r="R5" t="n">
-        <v>6874595</v>
+        <v>6874174</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,51 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111682945</v>
+        <v>131931528</v>
       </c>
       <c r="B6" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473691</v>
+        <v>473602</v>
       </c>
       <c r="R6" t="n">
-        <v>6874604</v>
+        <v>6874119</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1168,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111682935</v>
+        <v>131931837</v>
       </c>
       <c r="B7" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,35 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473691</v>
+        <v>473660</v>
       </c>
       <c r="R7" t="n">
-        <v>6874604</v>
+        <v>6874061</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1271,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111683326</v>
+        <v>119685301</v>
       </c>
       <c r="B8" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,35 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473524</v>
+        <v>473692</v>
       </c>
       <c r="R8" t="n">
-        <v>6874247</v>
+        <v>6874009</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1374,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1406,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112587715</v>
+        <v>119685145</v>
       </c>
       <c r="B9" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,38 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474059</v>
+        <v>473764</v>
       </c>
       <c r="R9" t="n">
-        <v>6874151</v>
+        <v>6873958</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1477,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,51 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112587824</v>
+        <v>119708207</v>
       </c>
       <c r="B10" t="n">
-        <v>78946</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473996</v>
+        <v>473610</v>
       </c>
       <c r="R10" t="n">
-        <v>6874182</v>
+        <v>6874206</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1580,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115981668</v>
+        <v>131932057</v>
       </c>
       <c r="B11" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brunnsbäcken, Hjd</t>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473700</v>
+        <v>473764</v>
       </c>
       <c r="R11" t="n">
-        <v>6874603</v>
+        <v>6874014</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1682,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1714,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118950384</v>
+        <v>119685308</v>
       </c>
       <c r="B12" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473490</v>
+        <v>473692</v>
       </c>
       <c r="R12" t="n">
-        <v>6874392</v>
+        <v>6874009</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1784,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,50 +1742,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118950660</v>
+        <v>111683326</v>
       </c>
       <c r="B13" t="n">
-        <v>78230</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen (Brännberget SO Byvallen), Hjd</t>
+          <t>Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473472</v>
+        <v>473523</v>
       </c>
       <c r="R13" t="n">
-        <v>6874447</v>
+        <v>6874246</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1886,12 +1808,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,37 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119685145</v>
+        <v>119706435</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,13 +1875,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473764</v>
+        <v>473673</v>
       </c>
       <c r="R14" t="n">
-        <v>6873958</v>
+        <v>6874029</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1988,12 +1905,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2020,15 +1937,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119685176</v>
+        <v>111682935</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,34 +1948,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473739</v>
+        <v>473691</v>
       </c>
       <c r="R15" t="n">
-        <v>6873984</v>
+        <v>6874603</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2090,12 +2003,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2122,15 +2035,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119685301</v>
+        <v>111683158</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,34 +2046,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473692</v>
+        <v>473472</v>
       </c>
       <c r="R16" t="n">
-        <v>6874009</v>
+        <v>6874259</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2192,12 +2101,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2224,15 +2133,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119685308</v>
+        <v>111682968</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,34 +2144,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473692</v>
+        <v>473689</v>
       </c>
       <c r="R17" t="n">
-        <v>6874009</v>
+        <v>6874595</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2294,12 +2199,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2326,15 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119706201</v>
+        <v>111683269</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,34 +2242,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473840</v>
+        <v>473502</v>
       </c>
       <c r="R18" t="n">
-        <v>6874139</v>
+        <v>6874253</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2396,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2428,50 +2329,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119705570</v>
+        <v>111683563</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473786</v>
+        <v>473804</v>
       </c>
       <c r="R19" t="n">
-        <v>6874355</v>
+        <v>6874287</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2498,12 +2395,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2530,15 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119708171</v>
+        <v>118950384</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,13 +2462,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473563</v>
+        <v>473490</v>
       </c>
       <c r="R20" t="n">
-        <v>6874196</v>
+        <v>6874392</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2600,12 +2492,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2632,50 +2524,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119706562</v>
+        <v>111682945</v>
       </c>
       <c r="B21" t="n">
-        <v>79642</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473620</v>
+        <v>473691</v>
       </c>
       <c r="R21" t="n">
-        <v>6874098</v>
+        <v>6874603</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2702,12 +2590,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2734,15 +2622,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119706557</v>
+        <v>111444632</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,37 +2633,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+          <t>Brunnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473620</v>
+        <v>473700</v>
       </c>
       <c r="R22" t="n">
-        <v>6874098</v>
+        <v>6874603</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2804,12 +2688,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2836,15 +2720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119705842</v>
+        <v>119705570</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2852,21 +2731,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2755,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473741</v>
+        <v>473786</v>
       </c>
       <c r="R23" t="n">
-        <v>6874202</v>
+        <v>6874355</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2938,37 +2817,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119706155</v>
+        <v>119685176</v>
       </c>
       <c r="B24" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2978,13 +2852,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473828</v>
+        <v>473739</v>
       </c>
       <c r="R24" t="n">
-        <v>6874124</v>
+        <v>6873984</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3008,12 +2882,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3040,37 +2914,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119708207</v>
+        <v>119706201</v>
       </c>
       <c r="B25" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,10 +2949,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473610</v>
+        <v>473840</v>
       </c>
       <c r="R25" t="n">
-        <v>6874206</v>
+        <v>6874139</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3142,37 +3011,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119705811</v>
+        <v>131930107</v>
       </c>
       <c r="B26" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3182,13 +3046,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473751</v>
+        <v>474008</v>
       </c>
       <c r="R26" t="n">
-        <v>6874222</v>
+        <v>6874146</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3212,12 +3076,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3244,32 +3113,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131931053</v>
+        <v>131930258</v>
       </c>
       <c r="B27" t="n">
-        <v>78993</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3279,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473669</v>
+        <v>473992</v>
       </c>
       <c r="R27" t="n">
-        <v>6874215</v>
+        <v>6874187</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3341,32 +3210,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131931837</v>
+        <v>131930506</v>
       </c>
       <c r="B28" t="n">
-        <v>78993</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3245,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473660</v>
+        <v>473888</v>
       </c>
       <c r="R28" t="n">
-        <v>6874061</v>
+        <v>6874110</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3438,14 +3307,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131930258</v>
+        <v>131930967</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3473,13 +3342,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473992</v>
+        <v>473719</v>
       </c>
       <c r="R29" t="n">
-        <v>6874187</v>
+        <v>6874196</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3538,11 +3407,11 @@
         <v>131931458</v>
       </c>
       <c r="B30" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3635,11 +3504,11 @@
         <v>131931861</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3729,32 +3598,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131932091</v>
+        <v>131931872</v>
       </c>
       <c r="B32" t="n">
-        <v>58114</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3764,13 +3633,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473755</v>
+        <v>473711</v>
       </c>
       <c r="R32" t="n">
-        <v>6874002</v>
+        <v>6874032</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3800,11 +3669,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3831,10 +3695,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131931505</v>
+        <v>131931493</v>
       </c>
       <c r="B33" t="n">
-        <v>79917</v>
+        <v>78776</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,21 +3706,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3730,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473596</v>
+        <v>473590</v>
       </c>
       <c r="R33" t="n">
-        <v>6874121</v>
+        <v>6874125</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3928,10 +3792,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131932307</v>
+        <v>131931945</v>
       </c>
       <c r="B34" t="n">
-        <v>79359</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,21 +3803,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3963,10 +3827,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473802</v>
+        <v>473714</v>
       </c>
       <c r="R34" t="n">
-        <v>6874032</v>
+        <v>6874034</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4025,10 +3889,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131931404</v>
+        <v>112587715</v>
       </c>
       <c r="B35" t="n">
-        <v>78334</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,34 +3900,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473585</v>
+        <v>474059</v>
       </c>
       <c r="R35" t="n">
-        <v>6874134</v>
+        <v>6874151</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4090,12 +3955,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4122,10 +3987,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131931410</v>
+        <v>115981668</v>
       </c>
       <c r="B36" t="n">
-        <v>79917</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,34 +3998,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+          <t>Brunnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473585</v>
+        <v>473700</v>
       </c>
       <c r="R36" t="n">
-        <v>6874134</v>
+        <v>6874603</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4187,12 +4052,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4219,10 +4084,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131930967</v>
+        <v>119705842</v>
       </c>
       <c r="B37" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4230,21 +4095,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4254,13 +4119,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473719</v>
+        <v>473741</v>
       </c>
       <c r="R37" t="n">
-        <v>6874196</v>
+        <v>6874202</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4284,12 +4149,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4316,10 +4181,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131931334</v>
+        <v>119706557</v>
       </c>
       <c r="B38" t="n">
-        <v>78993</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4327,21 +4192,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4351,10 +4216,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473561</v>
+        <v>473620</v>
       </c>
       <c r="R38" t="n">
-        <v>6874174</v>
+        <v>6874098</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4381,12 +4246,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4413,10 +4278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131931945</v>
+        <v>119708171</v>
       </c>
       <c r="B39" t="n">
-        <v>79946</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4424,21 +4289,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4448,13 +4313,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473714</v>
+        <v>473563</v>
       </c>
       <c r="R39" t="n">
-        <v>6874034</v>
+        <v>6874196</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4478,12 +4343,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4510,10 +4375,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131931681</v>
+        <v>131929938</v>
       </c>
       <c r="B40" t="n">
-        <v>80432</v>
+        <v>80488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4545,10 +4410,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473660</v>
+        <v>474075</v>
       </c>
       <c r="R40" t="n">
-        <v>6874125</v>
+        <v>6874149</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4581,6 +4446,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Mycket gammal sälgklon.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4607,10 +4477,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131929938</v>
+        <v>131931681</v>
       </c>
       <c r="B41" t="n">
-        <v>80432</v>
+        <v>80488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4642,10 +4512,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474075</v>
+        <v>473660</v>
       </c>
       <c r="R41" t="n">
-        <v>6874149</v>
+        <v>6874125</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4678,11 +4548,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Mycket gammal sälgklon.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4709,45 +4574,46 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131932057</v>
+        <v>112587824</v>
       </c>
       <c r="B42" t="n">
-        <v>79406</v>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+          <t>Brännberget SO Byvallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473764</v>
+        <v>473996</v>
       </c>
       <c r="R42" t="n">
-        <v>6874014</v>
+        <v>6874183</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4774,12 +4640,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4806,27 +4672,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131930107</v>
+        <v>119706562</v>
       </c>
       <c r="B43" t="n">
-        <v>79327</v>
+        <v>80467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4841,13 +4707,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474008</v>
+        <v>473620</v>
       </c>
       <c r="R43" t="n">
-        <v>6874146</v>
+        <v>6874098</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4871,17 +4737,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan.</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4908,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131931528</v>
+        <v>131931404</v>
       </c>
       <c r="B44" t="n">
-        <v>78993</v>
+        <v>78377</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4919,21 +4780,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4943,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473602</v>
+        <v>473585</v>
       </c>
       <c r="R44" t="n">
-        <v>6874119</v>
+        <v>6874134</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5005,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131930506</v>
+        <v>131931499</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>78377</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5016,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5040,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473888</v>
+        <v>473590</v>
       </c>
       <c r="R45" t="n">
-        <v>6874110</v>
+        <v>6874125</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5102,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131931872</v>
+        <v>131932091</v>
       </c>
       <c r="B46" t="n">
-        <v>79327</v>
+        <v>58136</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5113,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5137,13 +4998,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473711</v>
+        <v>473755</v>
       </c>
       <c r="R46" t="n">
-        <v>6874032</v>
+        <v>6874002</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5173,6 +5034,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Lockläte.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5196,6 +5062,394 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118950660</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>473472</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6874447</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>119705811</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>473751</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6874222</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131931410</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>473585</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6874134</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131931505</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Brännberget SO Byvallen, Brännberget SO Byvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>473596</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6874121</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
